--- a/research/traditional_assets/database/data/south_africa/south_africa_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0119</v>
+        <v>0.0372</v>
       </c>
       <c r="E2">
-        <v>-0.0144</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F2">
-        <v>0.2935</v>
+        <v>0.1635</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3463.94</v>
+        <v>4401.3</v>
       </c>
       <c r="L2">
-        <v>0.1922509962370545</v>
+        <v>0.2464568295974421</v>
       </c>
       <c r="M2">
-        <v>1082.3856</v>
+        <v>2002.2795</v>
       </c>
       <c r="N2">
-        <v>0.02575097542871281</v>
+        <v>0.04491863279769023</v>
       </c>
       <c r="O2">
-        <v>0.3124723869351086</v>
+        <v>0.4549291118533161</v>
       </c>
       <c r="P2">
-        <v>909.5456</v>
+        <v>1951.3395</v>
       </c>
       <c r="Q2">
-        <v>0.02163894863059325</v>
+        <v>0.04377585769825264</v>
       </c>
       <c r="R2">
-        <v>0.2625754487664336</v>
+        <v>0.4433552586735737</v>
       </c>
       <c r="S2">
-        <v>172.84</v>
+        <v>50.94</v>
       </c>
       <c r="T2">
-        <v>0.1596843121342338</v>
+        <v>0.02544100361612852</v>
       </c>
       <c r="U2">
-        <v>10382.3</v>
+        <v>11035.6</v>
       </c>
       <c r="V2">
-        <v>0.2470047201233323</v>
+        <v>0.2475698642982612</v>
       </c>
       <c r="W2">
-        <v>0.1366573376659967</v>
+        <v>0.1364885291555284</v>
       </c>
       <c r="X2">
-        <v>0.09844887262986546</v>
+        <v>0.1224034308778785</v>
       </c>
       <c r="Y2">
-        <v>0.03820846503613126</v>
+        <v>0.01408509827764992</v>
       </c>
       <c r="Z2">
-        <v>0.4224901967726905</v>
+        <v>0.379110669457266</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06328370823346077</v>
+        <v>0.09258808061760351</v>
       </c>
       <c r="AC2">
-        <v>-0.06328370823346077</v>
+        <v>-0.09258808061760351</v>
       </c>
       <c r="AD2">
-        <v>26566.7</v>
+        <v>26533</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26566.7</v>
+        <v>26533</v>
       </c>
       <c r="AG2">
-        <v>16184.4</v>
+        <v>15497.4</v>
       </c>
       <c r="AH2">
-        <v>0.3872725019861661</v>
+        <v>0.373132964039562</v>
       </c>
       <c r="AI2">
-        <v>0.4303658645240198</v>
+        <v>0.4446943553834112</v>
       </c>
       <c r="AJ2">
-        <v>0.2780003160577973</v>
+        <v>0.25797569960598</v>
       </c>
       <c r="AK2">
-        <v>0.3151892374026743</v>
+        <v>0.318679171953173</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.165</v>
+        <v>0.159</v>
       </c>
       <c r="E3">
-        <v>0.172</v>
+        <v>0.177</v>
       </c>
       <c r="F3">
-        <v>0.28</v>
+        <v>0.171</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>534.7</v>
+        <v>544.3</v>
       </c>
       <c r="L3">
-        <v>0.3706502148897824</v>
+        <v>0.3824480044969084</v>
       </c>
       <c r="M3">
-        <v>226.648</v>
+        <v>163.64</v>
       </c>
       <c r="N3">
-        <v>0.01533705964351933</v>
+        <v>0.01289326263207243</v>
       </c>
       <c r="O3">
-        <v>0.4238788105479707</v>
+        <v>0.3006430277420541</v>
       </c>
       <c r="P3">
-        <v>223.108</v>
+        <v>159.9</v>
       </c>
       <c r="Q3">
-        <v>0.01509751113156221</v>
+        <v>0.01259858650005121</v>
       </c>
       <c r="R3">
-        <v>0.4172582756685991</v>
+        <v>0.2937718170126769</v>
       </c>
       <c r="S3">
-        <v>3.539999999999992</v>
+        <v>3.740000000000009</v>
       </c>
       <c r="T3">
-        <v>0.01561893332392076</v>
+        <v>0.02285504766560749</v>
       </c>
       <c r="U3">
-        <v>2190.8</v>
+        <v>1560.7</v>
       </c>
       <c r="V3">
-        <v>0.1482494011287201</v>
+        <v>0.1229681923116318</v>
       </c>
       <c r="W3">
-        <v>0.3486794913596348</v>
+        <v>0.2473641156153426</v>
       </c>
       <c r="X3">
-        <v>0.05683713959120705</v>
+        <v>0.08873899684860023</v>
       </c>
       <c r="Y3">
-        <v>0.2918423517684278</v>
+        <v>0.1586251187667424</v>
       </c>
       <c r="Z3">
-        <v>-1.202096544368245</v>
+        <v>5.041623861985902</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05645042072045246</v>
+        <v>0.08821593060662318</v>
       </c>
       <c r="AC3">
-        <v>-0.05645042072045246</v>
+        <v>-0.08821593060662318</v>
       </c>
       <c r="AD3">
-        <v>269.1</v>
+        <v>247.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>269.1</v>
+        <v>247.6</v>
       </c>
       <c r="AG3">
-        <v>-1921.7</v>
+        <v>-1313.1</v>
       </c>
       <c r="AH3">
-        <v>0.01788408243558474</v>
+        <v>0.01913520615170602</v>
       </c>
       <c r="AI3">
-        <v>0.1088108042537706</v>
+        <v>0.1055458459439874</v>
       </c>
       <c r="AJ3">
-        <v>-0.149477679856255</v>
+        <v>-0.1153988118255001</v>
       </c>
       <c r="AK3">
-        <v>-6.807297201558633</v>
+        <v>-1.672312786551197</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00929</v>
+        <v>0.0304</v>
       </c>
       <c r="E4">
-        <v>-0.008920000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="F4">
-        <v>0.236</v>
+        <v>0.156</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1455.1</v>
+        <v>1833</v>
       </c>
       <c r="L4">
-        <v>0.1762988271784433</v>
+        <v>0.2305863409356799</v>
       </c>
       <c r="M4">
-        <v>667.254</v>
+        <v>1033.6095</v>
       </c>
       <c r="N4">
-        <v>0.0478757569669661</v>
+        <v>0.06353206385110424</v>
       </c>
       <c r="O4">
-        <v>0.4585622981238403</v>
+        <v>0.5638895253682488</v>
       </c>
       <c r="P4">
-        <v>667.254</v>
+        <v>1033.6095</v>
       </c>
       <c r="Q4">
-        <v>0.0478757569669661</v>
+        <v>0.06353206385110424</v>
       </c>
       <c r="R4">
-        <v>0.4585622981238403</v>
+        <v>0.5638895253682488</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5916.3</v>
+        <v>5923.8</v>
       </c>
       <c r="V4">
-        <v>0.4244970295324743</v>
+        <v>0.3641135649790093</v>
       </c>
       <c r="W4">
-        <v>0.1366573376659967</v>
+        <v>0.1364885291555284</v>
       </c>
       <c r="X4">
-        <v>0.07124902411084476</v>
+        <v>0.1046670939148219</v>
       </c>
       <c r="Y4">
-        <v>0.06540831355515196</v>
+        <v>0.03182143524070656</v>
       </c>
       <c r="Z4">
-        <v>0.5954892425794721</v>
+        <v>0.5326342591041575</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06028626976030312</v>
+        <v>0.09098247791778645</v>
       </c>
       <c r="AC4">
-        <v>-0.06028626976030312</v>
+        <v>-0.09098247791778645</v>
       </c>
       <c r="AD4">
-        <v>7025.5</v>
+        <v>7526.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7025.5</v>
+        <v>7526.9</v>
       </c>
       <c r="AG4">
-        <v>1109.2</v>
+        <v>1603.099999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3351428966688451</v>
+        <v>0.3163094637754244</v>
       </c>
       <c r="AI4">
-        <v>0.3097553878170082</v>
+        <v>0.3341590861668642</v>
       </c>
       <c r="AJ4">
-        <v>0.07371863037005527</v>
+        <v>0.08969796667450003</v>
       </c>
       <c r="AK4">
-        <v>0.06616361955322257</v>
+        <v>0.09656589021209436</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Absa Group Limited (JSE:ABG)</t>
+          <t>Nedbank Group Limited (JSE:NED)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.028</v>
+        <v>0.0372</v>
       </c>
       <c r="E5">
-        <v>-0.0144</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F5">
-        <v>0.307</v>
+        <v>0.149</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>949.9</v>
+        <v>786.1</v>
       </c>
       <c r="L5">
-        <v>0.1887418534414242</v>
+        <v>0.2340767650299259</v>
       </c>
       <c r="M5">
-        <v>75.3</v>
+        <v>399.6</v>
       </c>
       <c r="N5">
-        <v>0.009496065375302662</v>
+        <v>0.06558022746295111</v>
       </c>
       <c r="O5">
-        <v>0.07927150226339615</v>
+        <v>0.5083322732476784</v>
       </c>
       <c r="P5">
-        <v>13.9</v>
+        <v>369.1</v>
       </c>
       <c r="Q5">
-        <v>0.001752925746569814</v>
+        <v>0.0605747296210592</v>
       </c>
       <c r="R5">
-        <v>0.01463311927571323</v>
+        <v>0.4695331382775729</v>
       </c>
       <c r="S5">
-        <v>61.4</v>
+        <v>30.5</v>
       </c>
       <c r="T5">
-        <v>0.8154050464807437</v>
+        <v>0.07632632632632633</v>
       </c>
       <c r="U5">
-        <v>1136.6</v>
+        <v>2711.9</v>
       </c>
       <c r="V5">
-        <v>0.1433363599677159</v>
+        <v>0.4450626097516945</v>
       </c>
       <c r="W5">
-        <v>0.1418205706266143</v>
+        <v>0.1189078808047194</v>
       </c>
       <c r="X5">
-        <v>0.09844887262986546</v>
+        <v>0.1224034308778785</v>
       </c>
       <c r="Y5">
-        <v>0.04337169799674886</v>
+        <v>-0.00349555007315909</v>
       </c>
       <c r="Z5">
-        <v>0.2858035242741051</v>
+        <v>0.259807675942473</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06328370823346077</v>
+        <v>0.09258808061760351</v>
       </c>
       <c r="AC5">
-        <v>-0.06328370823346077</v>
+        <v>-0.09258808061760351</v>
       </c>
       <c r="AD5">
-        <v>11268.6</v>
+        <v>5825.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>11268.6</v>
+        <v>5825.8</v>
       </c>
       <c r="AG5">
-        <v>10132</v>
+        <v>3113.9</v>
       </c>
       <c r="AH5">
-        <v>0.5869612776197769</v>
+        <v>0.4887785151563457</v>
       </c>
       <c r="AI5">
-        <v>0.5373061738284602</v>
+        <v>0.457334400954579</v>
       </c>
       <c r="AJ5">
-        <v>0.5609691278734996</v>
+        <v>0.3382027109218872</v>
       </c>
       <c r="AK5">
-        <v>0.5107936155839442</v>
+        <v>0.3105608026569061</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nedbank Group Limited (JSE:NED)</t>
+          <t>Absa Group Limited (JSE:ABG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0119</v>
+        <v>0.0499</v>
       </c>
       <c r="E6">
-        <v>-0.0733</v>
+        <v>0.0585</v>
       </c>
       <c r="F6">
-        <v>0.357</v>
+        <v>0.255</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>518.8</v>
+        <v>1226.7</v>
       </c>
       <c r="L6">
-        <v>0.1615394196039357</v>
+        <v>0.2428483756656702</v>
       </c>
       <c r="M6">
-        <v>107.55</v>
+        <v>402.3</v>
       </c>
       <c r="N6">
-        <v>0.02020629015894488</v>
+        <v>0.04248869925224959</v>
       </c>
       <c r="O6">
-        <v>0.2073053199691596</v>
+        <v>0.3279530447542187</v>
       </c>
       <c r="P6">
-        <v>2.45</v>
+        <v>385.6</v>
       </c>
       <c r="Q6">
-        <v>0.0004603013564799158</v>
+        <v>0.04072493768746568</v>
       </c>
       <c r="R6">
-        <v>0.004722436391673092</v>
+        <v>0.3143392842585799</v>
       </c>
       <c r="S6">
-        <v>105.1</v>
+        <v>16.69999999999999</v>
       </c>
       <c r="T6">
-        <v>0.9772198977219897</v>
+        <v>0.04151130996768577</v>
       </c>
       <c r="U6">
-        <v>1058.2</v>
+        <v>794.5</v>
       </c>
       <c r="V6">
-        <v>0.1988126103783865</v>
+        <v>0.08391069240843226</v>
       </c>
       <c r="W6">
-        <v>0.1028487599865194</v>
+        <v>0.1439146859381966</v>
       </c>
       <c r="X6">
-        <v>0.09924108607804144</v>
+        <v>0.1360843048728981</v>
       </c>
       <c r="Y6">
-        <v>0.003607673908477979</v>
+        <v>0.007830381065298514</v>
       </c>
       <c r="Z6">
-        <v>0.2662333894272617</v>
+        <v>0.2707629798775715</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06333735255639031</v>
+        <v>0.09336329487344913</v>
       </c>
       <c r="AC6">
-        <v>-0.06333735255639031</v>
+        <v>-0.09336329487344913</v>
       </c>
       <c r="AD6">
-        <v>7706</v>
+        <v>12656.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>7706</v>
+        <v>12656.6</v>
       </c>
       <c r="AG6">
-        <v>6647.8</v>
+        <v>11862.1</v>
       </c>
       <c r="AH6">
-        <v>0.5914680011666641</v>
+        <v>0.5720497175141243</v>
       </c>
       <c r="AI6">
-        <v>0.5071672085401008</v>
+        <v>0.5838642266333907</v>
       </c>
       <c r="AJ6">
-        <v>0.5553532045712758</v>
+        <v>0.5561097958322589</v>
       </c>
       <c r="AK6">
-        <v>0.4702744765138653</v>
+        <v>0.5680320646656578</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.004500000000000001</v>
+        <v>0.0283</v>
       </c>
       <c r="E7">
-        <v>-0.201</v>
+        <v>-0.008789999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,85 +1231,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5.44</v>
+        <v>11.2</v>
       </c>
       <c r="L7">
-        <v>0.07046632124352332</v>
+        <v>0.1469816272965879</v>
       </c>
       <c r="M7">
-        <v>5.633599999999999</v>
+        <v>3.13</v>
       </c>
       <c r="N7">
-        <v>0.0858780487804878</v>
+        <v>0.0590566037735849</v>
       </c>
       <c r="O7">
-        <v>1.035588235294117</v>
+        <v>0.2794642857142857</v>
       </c>
       <c r="P7">
-        <v>2.8336</v>
+        <v>3.13</v>
       </c>
       <c r="Q7">
-        <v>0.04319512195121952</v>
+        <v>0.0590566037735849</v>
       </c>
       <c r="R7">
-        <v>0.5208823529411765</v>
+        <v>0.2794642857142857</v>
       </c>
       <c r="S7">
-        <v>2.799999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.4970178926441351</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>80.40000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="V7">
-        <v>1.225609756097561</v>
+        <v>0.8433962264150944</v>
       </c>
       <c r="W7">
-        <v>0.06146892655367232</v>
+        <v>0.1061611374407583</v>
       </c>
       <c r="X7">
-        <v>0.1908152740471429</v>
+        <v>0.2752835369274906</v>
       </c>
       <c r="Y7">
-        <v>-0.1293463474934706</v>
+        <v>-0.1691223994867323</v>
       </c>
       <c r="Z7">
-        <v>0.2457503024129369</v>
+        <v>0.2403179008452125</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06604967586296601</v>
+        <v>0.1028910751543719</v>
       </c>
       <c r="AC7">
-        <v>-0.06604967586296601</v>
+        <v>-0.1028910751543719</v>
       </c>
       <c r="AD7">
-        <v>297.5</v>
+        <v>276.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>297.5</v>
+        <v>276.1</v>
       </c>
       <c r="AG7">
-        <v>217.1</v>
+        <v>231.4</v>
       </c>
       <c r="AH7">
-        <v>0.8193335169374827</v>
+        <v>0.8389547250075965</v>
       </c>
       <c r="AI7">
-        <v>0.725609756097561</v>
+        <v>0.7284960422163589</v>
       </c>
       <c r="AJ7">
-        <v>0.7679518924655111</v>
+        <v>0.8136427566807314</v>
       </c>
       <c r="AK7">
-        <v>0.6586771844660193</v>
+        <v>0.6921926413401136</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/south_africa/south_africa_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0372</v>
+        <v>0.0529</v>
       </c>
       <c r="E2">
-        <v>0.05309999999999999</v>
+        <v>0.0885</v>
       </c>
       <c r="F2">
-        <v>0.1635</v>
+        <v>0.10185</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4401.3</v>
+        <v>4652.48</v>
       </c>
       <c r="L2">
-        <v>0.2464568295974421</v>
+        <v>0.2610365200217695</v>
       </c>
       <c r="M2">
-        <v>2002.2795</v>
+        <v>3003.6793</v>
       </c>
       <c r="N2">
-        <v>0.04491863279769023</v>
+        <v>0.06664653374396477</v>
       </c>
       <c r="O2">
-        <v>0.4549291118533161</v>
+        <v>0.6456082132540063</v>
       </c>
       <c r="P2">
-        <v>1951.3395</v>
+        <v>2468.6793</v>
       </c>
       <c r="Q2">
-        <v>0.04377585769825264</v>
+        <v>0.0547757938973303</v>
       </c>
       <c r="R2">
-        <v>0.4433552586735737</v>
+        <v>0.5306157791113556</v>
       </c>
       <c r="S2">
-        <v>50.94</v>
+        <v>535</v>
       </c>
       <c r="T2">
-        <v>0.02544100361612852</v>
+        <v>0.1781148872983877</v>
       </c>
       <c r="U2">
-        <v>11035.6</v>
+        <v>11704</v>
       </c>
       <c r="V2">
-        <v>0.2475698642982612</v>
+        <v>0.2596918489065606</v>
       </c>
       <c r="W2">
-        <v>0.1364885291555284</v>
+        <v>0.139996226177747</v>
       </c>
       <c r="X2">
-        <v>0.1224034308778785</v>
+        <v>0.09037648811313721</v>
       </c>
       <c r="Y2">
-        <v>0.01408509827764992</v>
+        <v>0.04961973806460983</v>
       </c>
       <c r="Z2">
-        <v>0.379110669457266</v>
+        <v>0.3607205221968471</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09258808061760351</v>
+        <v>0.07747495073113717</v>
       </c>
       <c r="AC2">
-        <v>-0.09258808061760351</v>
+        <v>-0.07747495073113717</v>
       </c>
       <c r="AD2">
-        <v>26533</v>
+        <v>27007.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26533</v>
+        <v>27007.3</v>
       </c>
       <c r="AG2">
-        <v>15497.4</v>
+        <v>15303.3</v>
       </c>
       <c r="AH2">
-        <v>0.373132964039562</v>
+        <v>0.3747053461549667</v>
       </c>
       <c r="AI2">
-        <v>0.4446943553834112</v>
+        <v>0.463045259869628</v>
       </c>
       <c r="AJ2">
-        <v>0.25797569960598</v>
+        <v>0.2534829830335535</v>
       </c>
       <c r="AK2">
-        <v>0.318679171953173</v>
+        <v>0.328246256011188</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,14 +713,14 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.159</v>
+        <v>0.136</v>
       </c>
       <c r="E3">
+        <v>0.156</v>
+      </c>
+      <c r="F3">
         <v>0.177</v>
       </c>
-      <c r="F3">
-        <v>0.171</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>544.3</v>
+        <v>533.2</v>
       </c>
       <c r="L3">
-        <v>0.3824480044969084</v>
+        <v>0.4008419786498271</v>
       </c>
       <c r="M3">
-        <v>163.64</v>
+        <v>276.382</v>
       </c>
       <c r="N3">
-        <v>0.01289326263207243</v>
+        <v>0.02154706125408322</v>
       </c>
       <c r="O3">
-        <v>0.3006430277420541</v>
+        <v>0.5183458364591147</v>
       </c>
       <c r="P3">
-        <v>159.9</v>
+        <v>265.182</v>
       </c>
       <c r="Q3">
-        <v>0.01259858650005121</v>
+        <v>0.02067389626488084</v>
       </c>
       <c r="R3">
-        <v>0.2937718170126769</v>
+        <v>0.4973405851462865</v>
       </c>
       <c r="S3">
-        <v>3.740000000000009</v>
+        <v>11.19999999999999</v>
       </c>
       <c r="T3">
-        <v>0.02285504766560749</v>
+        <v>0.04052362310135967</v>
       </c>
       <c r="U3">
-        <v>1560.7</v>
+        <v>1357.6</v>
       </c>
       <c r="V3">
-        <v>0.1229681923116318</v>
+        <v>0.1058400704768884</v>
       </c>
       <c r="W3">
-        <v>0.2473641156153426</v>
+        <v>0.2544742996229657</v>
       </c>
       <c r="X3">
-        <v>0.08873899684860023</v>
+        <v>0.0747318809660347</v>
       </c>
       <c r="Y3">
-        <v>0.1586251187667424</v>
+        <v>0.179742418656931</v>
       </c>
       <c r="Z3">
-        <v>5.041623861985902</v>
+        <v>1.694112253085241</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08821593060662318</v>
+        <v>0.07439020444212649</v>
       </c>
       <c r="AC3">
-        <v>-0.08821593060662318</v>
+        <v>-0.07439020444212649</v>
       </c>
       <c r="AD3">
-        <v>247.6</v>
+        <v>249.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>247.6</v>
+        <v>249.3</v>
       </c>
       <c r="AG3">
-        <v>-1313.1</v>
+        <v>-1108.3</v>
       </c>
       <c r="AH3">
-        <v>0.01913520615170602</v>
+        <v>0.01906517183891345</v>
       </c>
       <c r="AI3">
-        <v>0.1055458459439874</v>
+        <v>0.1069452189953241</v>
       </c>
       <c r="AJ3">
-        <v>-0.1153988118255001</v>
+        <v>-0.09457614390797535</v>
       </c>
       <c r="AK3">
-        <v>-1.672312786551197</v>
+        <v>-1.138469440164355</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0304</v>
+        <v>0.061</v>
       </c>
       <c r="E4">
-        <v>0.044</v>
+        <v>0.0888</v>
       </c>
       <c r="F4">
-        <v>0.156</v>
+        <v>0.106</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1833</v>
+        <v>2218.8</v>
       </c>
       <c r="L4">
-        <v>0.2305863409356799</v>
+        <v>0.2581320675694542</v>
       </c>
       <c r="M4">
-        <v>1033.6095</v>
+        <v>1393.6873</v>
       </c>
       <c r="N4">
-        <v>0.06353206385110424</v>
+        <v>0.07388275240543907</v>
       </c>
       <c r="O4">
-        <v>0.5638895253682488</v>
+        <v>0.6281265999639444</v>
       </c>
       <c r="P4">
-        <v>1033.6095</v>
+        <v>1215.3873</v>
       </c>
       <c r="Q4">
-        <v>0.06353206385110424</v>
+        <v>0.06443063588411482</v>
       </c>
       <c r="R4">
-        <v>0.5638895253682488</v>
+        <v>0.547767847485127</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>178.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.1279340064302803</v>
       </c>
       <c r="U4">
-        <v>5923.8</v>
+        <v>7255.1</v>
       </c>
       <c r="V4">
-        <v>0.3641135649790093</v>
+        <v>0.3846104911601771</v>
       </c>
       <c r="W4">
-        <v>0.1364885291555284</v>
+        <v>0.1650671785028791</v>
       </c>
       <c r="X4">
-        <v>0.1046670939148219</v>
+        <v>0.08426727921158747</v>
       </c>
       <c r="Y4">
-        <v>0.03182143524070656</v>
+        <v>0.08079989929129164</v>
       </c>
       <c r="Z4">
-        <v>0.5326342591041575</v>
+        <v>0.5588416953273823</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09098247791778645</v>
+        <v>0.07659029840226539</v>
       </c>
       <c r="AC4">
-        <v>-0.09098247791778645</v>
+        <v>-0.07659029840226539</v>
       </c>
       <c r="AD4">
-        <v>7526.9</v>
+        <v>7321.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7526.9</v>
+        <v>7321.3</v>
       </c>
       <c r="AG4">
-        <v>1603.099999999999</v>
+        <v>66.19999999999982</v>
       </c>
       <c r="AH4">
-        <v>0.3163094637754244</v>
+        <v>0.2796011426476429</v>
       </c>
       <c r="AI4">
-        <v>0.3341590861668642</v>
+        <v>0.3363007060142122</v>
       </c>
       <c r="AJ4">
-        <v>0.08969796667450003</v>
+        <v>0.003497149981246392</v>
       </c>
       <c r="AK4">
-        <v>0.09656589021209436</v>
+        <v>0.00456079917326902</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0372</v>
+        <v>0.0391</v>
       </c>
       <c r="E5">
-        <v>0.05309999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="F5">
-        <v>0.149</v>
+        <v>0.0977</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>786.1</v>
+        <v>781.8</v>
       </c>
       <c r="L5">
-        <v>0.2340767650299259</v>
+        <v>0.2475617479417353</v>
       </c>
       <c r="M5">
-        <v>399.6</v>
+        <v>736.5</v>
       </c>
       <c r="N5">
-        <v>0.06558022746295111</v>
+        <v>0.1340309372156506</v>
       </c>
       <c r="O5">
-        <v>0.5083322732476784</v>
+        <v>0.9420567920184191</v>
       </c>
       <c r="P5">
-        <v>369.1</v>
+        <v>443</v>
       </c>
       <c r="Q5">
-        <v>0.0605747296210592</v>
+        <v>0.08061874431301183</v>
       </c>
       <c r="R5">
-        <v>0.4695331382775729</v>
+        <v>0.5666410846763879</v>
       </c>
       <c r="S5">
-        <v>30.5</v>
+        <v>293.5</v>
       </c>
       <c r="T5">
-        <v>0.07632632632632633</v>
+        <v>0.3985064494229464</v>
       </c>
       <c r="U5">
-        <v>2711.9</v>
+        <v>2370</v>
       </c>
       <c r="V5">
-        <v>0.4450626097516945</v>
+        <v>0.4313011828935396</v>
       </c>
       <c r="W5">
-        <v>0.1189078808047194</v>
+        <v>0.1252824383443104</v>
       </c>
       <c r="X5">
-        <v>0.1224034308778785</v>
+        <v>0.09037648811313721</v>
       </c>
       <c r="Y5">
-        <v>-0.00349555007315909</v>
+        <v>0.03490595023117314</v>
       </c>
       <c r="Z5">
-        <v>0.259807675942473</v>
+        <v>0.3376023604370229</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09258808061760351</v>
+        <v>0.07747495073113717</v>
       </c>
       <c r="AC5">
-        <v>-0.09258808061760351</v>
+        <v>-0.07747495073113717</v>
       </c>
       <c r="AD5">
-        <v>5825.8</v>
+        <v>3430.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5825.8</v>
+        <v>3430.7</v>
       </c>
       <c r="AG5">
-        <v>3113.9</v>
+        <v>1060.7</v>
       </c>
       <c r="AH5">
-        <v>0.4887785151563457</v>
+        <v>0.3843620108226805</v>
       </c>
       <c r="AI5">
-        <v>0.457334400954579</v>
+        <v>0.3560479476934253</v>
       </c>
       <c r="AJ5">
-        <v>0.3382027109218872</v>
+        <v>0.1617981298717147</v>
       </c>
       <c r="AK5">
-        <v>0.3105608026569061</v>
+        <v>0.1459913288830775</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0499</v>
+        <v>0.0529</v>
       </c>
       <c r="E6">
-        <v>0.0585</v>
+        <v>0.0885</v>
       </c>
       <c r="F6">
-        <v>0.255</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1226.7</v>
+        <v>1112.9</v>
       </c>
       <c r="L6">
-        <v>0.2428483756656702</v>
+        <v>0.2382981456896921</v>
       </c>
       <c r="M6">
-        <v>402.3</v>
+        <v>595.1</v>
       </c>
       <c r="N6">
-        <v>0.04248869925224959</v>
+        <v>0.07588722120914575</v>
       </c>
       <c r="O6">
-        <v>0.3279530447542187</v>
+        <v>0.5347290861712642</v>
       </c>
       <c r="P6">
-        <v>385.6</v>
+        <v>543.1</v>
       </c>
       <c r="Q6">
-        <v>0.04072493768746568</v>
+        <v>0.06925617516163175</v>
       </c>
       <c r="R6">
-        <v>0.3143392842585799</v>
+        <v>0.4880043130559799</v>
       </c>
       <c r="S6">
-        <v>16.69999999999999</v>
+        <v>52</v>
       </c>
       <c r="T6">
-        <v>0.04151130996768577</v>
+        <v>0.08738027222315577</v>
       </c>
       <c r="U6">
-        <v>794.5</v>
+        <v>683.5</v>
       </c>
       <c r="V6">
-        <v>0.08391069240843226</v>
+        <v>0.08715999948991954</v>
       </c>
       <c r="W6">
-        <v>0.1439146859381966</v>
+        <v>0.139996226177747</v>
       </c>
       <c r="X6">
-        <v>0.1360843048728981</v>
+        <v>0.1262107961773966</v>
       </c>
       <c r="Y6">
-        <v>0.007830381065298514</v>
+        <v>0.01378543000035043</v>
       </c>
       <c r="Z6">
-        <v>0.2707629798775715</v>
+        <v>0.1982594668025132</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09336329487344913</v>
+        <v>0.07986808877262624</v>
       </c>
       <c r="AC6">
-        <v>-0.09336329487344913</v>
+        <v>-0.07986808877262624</v>
       </c>
       <c r="AD6">
-        <v>12656.6</v>
+        <v>15761.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12656.6</v>
+        <v>15761.1</v>
       </c>
       <c r="AG6">
-        <v>11862.1</v>
+        <v>15077.6</v>
       </c>
       <c r="AH6">
-        <v>0.5720497175141243</v>
+        <v>0.6677583358047706</v>
       </c>
       <c r="AI6">
-        <v>0.5838642266333907</v>
+        <v>0.6497814973614776</v>
       </c>
       <c r="AJ6">
-        <v>0.5561097958322589</v>
+        <v>0.6578503021444622</v>
       </c>
       <c r="AK6">
-        <v>0.5680320646656578</v>
+        <v>0.6396266836355924</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0283</v>
+        <v>0.039</v>
       </c>
       <c r="E7">
-        <v>-0.008789999999999999</v>
+        <v>-0.0356</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,28 +1231,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>11.2</v>
+        <v>5.78</v>
       </c>
       <c r="L7">
-        <v>0.1469816272965879</v>
+        <v>0.08364688856729378</v>
       </c>
       <c r="M7">
-        <v>3.13</v>
+        <v>2.01</v>
       </c>
       <c r="N7">
-        <v>0.0590566037735849</v>
+        <v>0.04843373493975903</v>
       </c>
       <c r="O7">
-        <v>0.2794642857142857</v>
+        <v>0.3477508650519031</v>
       </c>
       <c r="P7">
-        <v>3.13</v>
+        <v>2.01</v>
       </c>
       <c r="Q7">
-        <v>0.0590566037735849</v>
+        <v>0.04843373493975903</v>
       </c>
       <c r="R7">
-        <v>0.2794642857142857</v>
+        <v>0.3477508650519031</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1261,55 +1261,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>44.7</v>
+        <v>37.8</v>
       </c>
       <c r="V7">
-        <v>0.8433962264150944</v>
+        <v>0.9108433734939758</v>
       </c>
       <c r="W7">
-        <v>0.1061611374407583</v>
+        <v>0.05977249224405377</v>
       </c>
       <c r="X7">
-        <v>0.2752835369274906</v>
+        <v>0.226853971456106</v>
       </c>
       <c r="Y7">
-        <v>-0.1691223994867323</v>
+        <v>-0.1670814792120522</v>
       </c>
       <c r="Z7">
-        <v>0.2403179008452125</v>
+        <v>0.2073642829277076</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1028910751543719</v>
+        <v>0.08674409654288345</v>
       </c>
       <c r="AC7">
-        <v>-0.1028910751543719</v>
+        <v>-0.08674409654288345</v>
       </c>
       <c r="AD7">
-        <v>276.1</v>
+        <v>244.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>276.1</v>
+        <v>244.9</v>
       </c>
       <c r="AG7">
-        <v>231.4</v>
+        <v>207.1</v>
       </c>
       <c r="AH7">
-        <v>0.8389547250075965</v>
+        <v>0.8550977653631285</v>
       </c>
       <c r="AI7">
-        <v>0.7284960422163589</v>
+        <v>0.7360985873159003</v>
       </c>
       <c r="AJ7">
-        <v>0.8136427566807314</v>
+        <v>0.833065164923572</v>
       </c>
       <c r="AK7">
-        <v>0.6921926413401136</v>
+        <v>0.702271956595456</v>
       </c>
       <c r="AL7">
         <v>0</v>
